--- a/public/planilhas/03_metas_e_habitos.xlsx
+++ b/public/planilhas/03_metas_e_habitos.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAINEL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METAS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HABITOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,12 +34,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000A1322"/>
-      <sz val="18"/>
+      <color rgb="00C99C66"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005C6B82"/>
+      <b val="1"/>
+      <color rgb="000A1322"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008593A8"/>
       <sz val="11"/>
     </font>
     <font>
@@ -49,7 +55,20 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="008593A8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A1322"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008593A8"/>
     </font>
   </fonts>
   <fills count="4">
@@ -66,7 +85,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F1EA"/>
+        <fgColor rgb="00F8F4EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,32 +99,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -222,7 +249,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'METAS'!D4</f>
+              <f>'METAS'!D5</f>
             </strRef>
           </tx>
           <spPr>
@@ -232,12 +259,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'METAS'!$A$5:$A$9</f>
+              <f>'METAS'!$A$6:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'METAS'!$D$5:$D$9</f>
+              <f>'METAS'!$D$6:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -281,12 +308,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5400000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -593,75 +620,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Painel Metas &amp; Hábitos</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Visão executiva automática</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Metas em andamento</t>
-        </is>
-      </c>
-      <c r="B4" s="4">
-        <f>COUNTA(METAS!A5:A50)</f>
-        <v/>
-      </c>
-    </row>
+          <t>Dashboard Metas &amp; Hábitos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Progresso, consistência e ranking visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Progresso médio das metas</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>METAS ATIVAS</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>IFERROR(AVERAGE(METAS!D5:D50),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Hábitos ativos</t>
-        </is>
-      </c>
-      <c r="B6" s="4">
-        <f>COUNTA(HABITOS!A5:A50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Consistência média</t>
-        </is>
-      </c>
-      <c r="B7" s="5">
-        <f>IFERROR(AVERAGE(HABITOS!I5:I50),0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTA(METAS!A6:A50)</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PROGRESSO MÉDIO</t>
+        </is>
+      </c>
+      <c r="D5" s="6">
+        <f>IFERROR(AVERAGE(METAS!D6:D50),0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>HÁBITOS</t>
+        </is>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTA(HABITOS!A6:A50)</f>
+        <v/>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CONSISTÊNCIA</t>
+        </is>
+      </c>
+      <c r="H5" s="6">
+        <f>IFERROR(AVERAGE(HABITOS!I6:I50),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>
@@ -674,17 +707,22 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Ritual: 10 minutos no domingo para atualizar Realizado e marcar hábitos. A planilha faz o resto.</t>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Ritual TrustCorp: 10 minutos no domingo. Atualize Realizado e marque hábitos. O dashboard faz o resto.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -700,368 +738,361 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Metas do Ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Metas do Ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>Progresso automático com barra visual</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Valor-alvo</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Realizado</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>% Progresso</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Barra</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Barra visual</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Por quê</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Faturar R$ 30 mil/mês</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>18500</v>
-      </c>
-      <c r="D5" s="5">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="4">
-        <f>REPT("█",ROUNDDOWN(D5*10,0))&amp;REPT("░",10-ROUNDDOWN(D5*10,0))</f>
-        <v/>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="C6" s="9" t="n">
+        <v>19200</v>
+      </c>
+      <c r="D6" s="10">
+        <f>IF(B6=0,0,C6/B6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>REPT("█",ROUNDDOWN(D6*12,0))&amp;REPT("░",12-ROUNDDOWN(D6*12,0))</f>
+        <v/>
+      </c>
+      <c r="F6" s="11" t="n">
         <v>46387</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Liberdade financeira</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Criar reserva de emergência</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D6" s="5">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="4">
-        <f>REPT("█",ROUNDDOWN(D6*10,0))&amp;REPT("░",10-ROUNDDOWN(D6*10,0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="C7" s="9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D7" s="10">
+        <f>IF(B7=0,0,C7/B7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>REPT("█",ROUNDDOWN(D7*12,0))&amp;REPT("░",12-ROUNDDOWN(D7*12,0))</f>
+        <v/>
+      </c>
+      <c r="F7" s="11" t="n">
         <v>46296</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Segurança</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Reduzir assinaturas</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Reduzir assinaturas ociosas</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" s="5">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="4">
-        <f>REPT("█",ROUNDDOWN(D7*10,0))&amp;REPT("░",10-ROUNDDOWN(D7*10,0))</f>
-        <v/>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="C8" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="D8" s="10">
+        <f>IF(B8=0,0,C8/B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
+        <f>REPT("█",ROUNDDOWN(D8*12,0))&amp;REPT("░",12-ROUNDDOWN(D8*12,0))</f>
+        <v/>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>46265</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Estancar vazamento</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Ler 12 livros</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="4">
-        <f>REPT("█",ROUNDDOWN(D8*10,0))&amp;REPT("░",10-ROUNDDOWN(D8*10,0))</f>
-        <v/>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="C9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="10">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
+        <f>REPT("█",ROUNDDOWN(D9*12,0))&amp;REPT("░",12-ROUNDDOWN(D9*12,0))</f>
+        <v/>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>46387</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Clareza e foco</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Fechar 8 novos clientes</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="4">
-        <f>REPT("█",ROUNDDOWN(D9*10,0))&amp;REPT("░",10-ROUNDDOWN(D9*10,0))</f>
-        <v/>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="C10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="10">
+        <f>IF(B10=0,0,C10/B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="9">
+        <f>REPT("█",ROUNDDOWN(D10*12,0))&amp;REPT("░",12-ROUNDDOWN(D10*12,0))</f>
+        <v/>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>46387</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Crescimento comercial</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="5">
-        <f>IF(OR(B10="",B10=0),"",C10/B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="4">
-        <f>IF(D10="","",REPT("█",ROUNDDOWN(D10*10,0))&amp;REPT("░",10-ROUNDDOWN(D10*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="4" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="5">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10">
         <f>IF(OR(B11="",B11=0),"",C11/B11)</f>
         <v/>
       </c>
-      <c r="E11" s="4">
-        <f>IF(D11="","",REPT("█",ROUNDDOWN(D11*10,0))&amp;REPT("░",10-ROUNDDOWN(D11*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="E11" s="9">
+        <f>IF(D11="","",REPT("█",ROUNDDOWN(D11*12,0))&amp;REPT("░",12-ROUNDDOWN(D11*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="5">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10">
         <f>IF(OR(B12="",B12=0),"",C12/B12)</f>
         <v/>
       </c>
-      <c r="E12" s="4">
-        <f>IF(D12="","",REPT("█",ROUNDDOWN(D12*10,0))&amp;REPT("░",10-ROUNDDOWN(D12*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="E12" s="9">
+        <f>IF(D12="","",REPT("█",ROUNDDOWN(D12*12,0))&amp;REPT("░",12-ROUNDDOWN(D12*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10">
         <f>IF(OR(B13="",B13=0),"",C13/B13)</f>
         <v/>
       </c>
-      <c r="E13" s="4">
-        <f>IF(D13="","",REPT("█",ROUNDDOWN(D13*10,0))&amp;REPT("░",10-ROUNDDOWN(D13*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="E13" s="9">
+        <f>IF(D13="","",REPT("█",ROUNDDOWN(D13*12,0))&amp;REPT("░",12-ROUNDDOWN(D13*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="5">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10">
         <f>IF(OR(B14="",B14=0),"",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="4">
-        <f>IF(D14="","",REPT("█",ROUNDDOWN(D14*10,0))&amp;REPT("░",10-ROUNDDOWN(D14*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="E14" s="9">
+        <f>IF(D14="","",REPT("█",ROUNDDOWN(D14*12,0))&amp;REPT("░",12-ROUNDDOWN(D14*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10">
         <f>IF(OR(B15="",B15=0),"",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="4">
-        <f>IF(D15="","",REPT("█",ROUNDDOWN(D15*10,0))&amp;REPT("░",10-ROUNDDOWN(D15*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="E15" s="9">
+        <f>IF(D15="","",REPT("█",ROUNDDOWN(D15*12,0))&amp;REPT("░",12-ROUNDDOWN(D15*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10">
         <f>IF(OR(B16="",B16=0),"",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="4">
-        <f>IF(D16="","",REPT("█",ROUNDDOWN(D16*10,0))&amp;REPT("░",10-ROUNDDOWN(D16*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="E16" s="9">
+        <f>IF(D16="","",REPT("█",ROUNDDOWN(D16*12,0))&amp;REPT("░",12-ROUNDDOWN(D16*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10">
         <f>IF(OR(B17="",B17=0),"",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="4">
-        <f>IF(D17="","",REPT("█",ROUNDDOWN(D17*10,0))&amp;REPT("░",10-ROUNDDOWN(D17*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="E17" s="9">
+        <f>IF(D17="","",REPT("█",ROUNDDOWN(D17*12,0))&amp;REPT("░",12-ROUNDDOWN(D17*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="5">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10">
         <f>IF(OR(B18="",B18=0),"",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="4">
-        <f>IF(D18="","",REPT("█",ROUNDDOWN(D18*10,0))&amp;REPT("░",10-ROUNDDOWN(D18*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="E18" s="9">
+        <f>IF(D18="","",REPT("█",ROUNDDOWN(D18*12,0))&amp;REPT("░",12-ROUNDDOWN(D18*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="5">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10">
         <f>IF(OR(B19="",B19=0),"",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="4">
-        <f>IF(D19="","",REPT("█",ROUNDDOWN(D19*10,0))&amp;REPT("░",10-ROUNDDOWN(D19*10,0)))</f>
-        <v/>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="E19" s="9">
+        <f>IF(D19="","",REPT("█",ROUNDDOWN(D19*12,0))&amp;REPT("░",12-ROUNDDOWN(D19*12,0)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D19">
+  <conditionalFormatting sqref="D6:D19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1083,10 +1114,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1094,295 +1125,283 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Hábitos da Semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Marque x nos dias cumpridos · consistência automática</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+          <t>Hábitos da Semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Marque x · consistência automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Hábito</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Seg</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Ter</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Qua</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Qui</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Sáb</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>% Semana</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Treinar</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I5" s="5">
-        <f>COUNTIF(B5:H5,"x")/7</f>
-        <v/>
-      </c>
-      <c r="J5" s="4">
-        <f>IF(I5&gt;=0.8,"🔥 Consistente",IF(I5&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="10">
+        <f>COUNTIF(B6:H6,"x")/7</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>IF(I6&gt;=0.8,"🔥 Consistente",IF(I6&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Ler 20 min</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I6" s="5">
-        <f>COUNTIF(B6:H6,"x")/7</f>
-        <v/>
-      </c>
-      <c r="J6" s="4">
-        <f>IF(I6&gt;=0.8,"🔥 Consistente",IF(I6&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I7" s="10">
+        <f>COUNTIF(B7:H7,"x")/7</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>IF(I7&gt;=0.8,"🔥 Consistente",IF(I7&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Prospecção comercial</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I7" s="5">
-        <f>COUNTIF(B7:H7,"x")/7</f>
-        <v/>
-      </c>
-      <c r="J7" s="4">
-        <f>IF(I7&gt;=0.8,"🔥 Consistente",IF(I7&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" s="10">
+        <f>COUNTIF(B8:H8,"x")/7</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>IF(I8&gt;=0.8,"🔥 Consistente",IF(I8&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Registrar finanças</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I8" s="5">
-        <f>COUNTIF(B8:H8,"x")/7</f>
-        <v/>
-      </c>
-      <c r="J8" s="4">
-        <f>IF(I8&gt;=0.8,"🔥 Consistente",IF(I8&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I9" s="10">
+        <f>COUNTIF(B9:H9,"x")/7</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>IF(I9&gt;=0.8,"🔥 Consistente",IF(I9&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Dormir 7h</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I9" s="5">
-        <f>COUNTIF(B9:H9,"x")/7</f>
-        <v/>
-      </c>
-      <c r="J9" s="4">
-        <f>IF(I9&gt;=0.8,"🔥 Consistente",IF(I9&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="10">
+        <f>COUNTIF(B10:H10,"x")/7</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>IF(I10&gt;=0.8,"🔥 Consistente",IF(I10&gt;=0.5,"Em progresso","⚠ Frágil"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:H50">
+  <conditionalFormatting sqref="B6:H50">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B5="x"</formula>
+      <formula>B6="x"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
